--- a/test_cases.xlsx
+++ b/test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GOWSHI\Documents\database-testing-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23DA5565-4226-4F87-A29D-B61A7FD7B25F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97DE6BD-5FE7-4E58-8282-2262B1D75FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6F704409-A403-4604-A8AA-EE9849DD2930}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="65">
   <si>
     <t>Test ID</t>
   </si>
@@ -162,6 +162,96 @@
       </rPr>
       <t>) &gt; 1;</t>
     </r>
+  </si>
+  <si>
+    <t>T11</t>
+  </si>
+  <si>
+    <t>Every customer has a matching address</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM customer JOIN address ON customer.address_id = address.address_id;</t>
+  </si>
+  <si>
+    <t>T12</t>
+  </si>
+  <si>
+    <t>Every film has a matching language</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM film JOIN language ON film.language_id = language.language_id;</t>
+  </si>
+  <si>
+    <t>T13</t>
+  </si>
+  <si>
+    <t>Every payment belongs to an existing customer</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM payment JOIN customer ON payment.customer_id = customer.customer_id;</t>
+  </si>
+  <si>
+    <t>T14</t>
+  </si>
+  <si>
+    <t>Every inventory item belongs to an existing film</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM inventory JOIN film ON inventory.film_id = film.film_id;</t>
+  </si>
+  <si>
+    <t>T15</t>
+  </si>
+  <si>
+    <t>Every rental belongs to an existing customer</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM rental JOIN customer ON rental.customer_id = customer.customer_id;</t>
+  </si>
+  <si>
+    <t>T16</t>
+  </si>
+  <si>
+    <t>No rental has a return date before its rental date</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM rental WHERE return_date &lt; rental_date;</t>
+  </si>
+  <si>
+    <t>T17</t>
+  </si>
+  <si>
+    <t>No film has a replacement cost lower than its rental rate</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM film WHERE replacement_cost &lt; rental_rate;</t>
+  </si>
+  <si>
+    <t>T18</t>
+  </si>
+  <si>
+    <t>Each payment belongs to the same customer as its rental</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM payment JOIN rental ON payment.rental_id = rental.rental_id WHERE payment.customer_id &lt;&gt; rental.customer_id;</t>
+  </si>
+  <si>
+    <t>T19</t>
+  </si>
+  <si>
+    <t>Every rental points to an existing inventory item</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM rental JOIN inventory ON rental.inventory_id = inventory.inventory_id;</t>
+  </si>
+  <si>
+    <t>T20</t>
+  </si>
+  <si>
+    <t>No film has a length of zero or less</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM film WHERE length &lt;= 0;</t>
   </si>
 </sst>
 </file>
@@ -219,16 +309,16 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -565,19 +655,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3844F5-5B4E-4DEE-A6DD-8CE9A0802742}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="37.77734375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="86.88671875" style="2" customWidth="1"/>
     <col min="4" max="4" width="17.88671875" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.77734375" style="2" customWidth="1"/>
     <col min="6" max="6" width="17" style="2" customWidth="1"/>
     <col min="7" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -597,7 +687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -617,7 +707,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -637,7 +727,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
@@ -657,7 +747,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>16</v>
       </c>
@@ -677,7 +767,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>19</v>
       </c>
@@ -697,7 +787,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>22</v>
       </c>
@@ -717,7 +807,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -737,7 +827,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
@@ -757,7 +847,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>31</v>
       </c>
@@ -774,6 +864,206 @@
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="2">
+        <v>599</v>
+      </c>
+      <c r="E11" s="2">
+        <v>599</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="2">
+        <v>16044</v>
+      </c>
+      <c r="E13" s="2">
+        <v>16044</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="2">
+        <v>4581</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4581</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="2">
+        <v>16044</v>
+      </c>
+      <c r="E15" s="2">
+        <v>16044</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="2">
+        <v>16044</v>
+      </c>
+      <c r="E19" s="2">
+        <v>16044</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>9</v>
       </c>
     </row>
